--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE62E49-04BF-4CB0-A190-326CD25600DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B05262-CD50-409E-8E86-81704D99F2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31010" yWindow="580" windowWidth="28800" windowHeight="15690" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
   <si>
     <t>Mission Time</t>
   </si>
@@ -75,6 +75,45 @@
   </si>
   <si>
     <t>Conduct Geological Survey</t>
+  </si>
+  <si>
+    <t>Sub-faction</t>
+  </si>
+  <si>
+    <t>Spore Burst Strain</t>
+  </si>
+  <si>
+    <t>Cyborgs</t>
+  </si>
+  <si>
+    <t>Planet</t>
+  </si>
+  <si>
+    <t>Marfark</t>
+  </si>
+  <si>
+    <t>City?</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Gatria</t>
+  </si>
+  <si>
+    <t>Halt Cyborg Production</t>
+  </si>
+  <si>
+    <t>Success?</t>
+  </si>
+  <si>
+    <t>Difficulty</t>
+  </si>
+  <si>
+    <t>Dutch Squad?</t>
   </si>
 </sst>
 </file>
@@ -82,7 +121,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="mm:ss.0;@"/>
+    <numFmt numFmtId="164" formatCode="mm:ss.0;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -124,7 +163,7 @@
     <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -461,18 +500,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B874BC27-9F05-4CCB-84C0-24A63EA21ED1}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.90625" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" customWidth="1"/>
-    <col min="3" max="3" width="22.08984375" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -480,19 +525,37 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>46218</v>
       </c>
@@ -500,19 +563,37 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3">
+      <c r="F2" s="3">
         <v>8.3333333333333332E-3</v>
       </c>
-      <c r="E2" s="1">
+      <c r="G2" s="1">
         <v>20</v>
       </c>
-      <c r="F2" s="1">
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>46218</v>
       </c>
@@ -520,19 +601,37 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3">
+      <c r="F3" s="3">
         <v>1.02430555555556</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>20</v>
       </c>
-      <c r="F3" s="1">
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>46218</v>
       </c>
@@ -540,19 +639,37 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3">
+      <c r="F4" s="3">
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="1">
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>46218</v>
       </c>
@@ -560,272 +677,444 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3">
+      <c r="F5" s="3">
         <v>1.5680555555555555</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>40</v>
       </c>
-      <c r="F5" s="1">
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.7592592592592592E-2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="3"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="3"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="3"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="3"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="3"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="3"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="3"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="3"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="3"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="3"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="3"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="3"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="3"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="3"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="3"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="3"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="4"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="4"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="4"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="4"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="4"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="4"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
       <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Terminid;Automatons; Illuminates" sqref="B2:B37" xr:uid="{D798BB62-A9AA-484F-B0C1-2284059A6DE0}">
       <formula1>"Terminids, Automatons, lluminate"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C38" xr:uid="{7F86A978-3145-4566-A41E-75F6734EC977}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C37:C38" xr:uid="{7F86A978-3145-4566-A41E-75F6734EC977}">
       <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I7" xr:uid="{8401F6A8-3ACC-45FE-A6B4-ABFE7E6BEC32}">
+      <formula1>"No, Yes"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K7" xr:uid="{164DCC27-42E4-47D3-A8E6-BB0649B15D98}">
+      <formula1>"Yes, No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C7 F8:F39" xr:uid="{CBAA832B-00A1-4E19-BB8D-1F53FBB66E4C}">
+      <formula1>"N/A, Incineration Corps, Cyborgs, Predator Strain, Rupture Strain, Spore Burst Strain, Mindless Masses, Appropriators"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E7 C8:C36" xr:uid="{7FABB6A8-04E9-4E50-B186-49920BF7CE6B}">
+      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D36" xr:uid="{628F7E99-C793-498B-BB51-F86A87D5EBDA}">
+      <formula1>"10, 9, 8, 7, 6, 5, 4, 3, 2, 1"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B05262-CD50-409E-8E86-81704D99F2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530E29EC-3056-4B23-B070-648578743D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31010" yWindow="580" windowWidth="28800" windowHeight="15690" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="26">
   <si>
     <t>Mission Time</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>Dutch Squad?</t>
+  </si>
+  <si>
+    <t>Eradicate</t>
   </si>
 </sst>
 </file>
@@ -500,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B874BC27-9F05-4CCB-84C0-24A63EA21ED1}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -784,84 +787,308 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="A8" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1.5902777777777776E-2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="A9" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5.7094907407407407E-2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="A10" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1.4502314814814815E-2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="A11" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1.4965277777777777E-2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="A12" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>5.6805555555555554E-2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="1">
+        <v>8</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="A13" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2.1956018518518517E-2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="A14" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2.1354166666666667E-2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="A15" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>5.9837962962962961E-3</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -869,7 +1096,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
@@ -879,7 +1106,7 @@
       <c r="C17" s="1"/>
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
@@ -889,7 +1116,7 @@
       <c r="C18" s="1"/>
       <c r="D18" s="3"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="F18" s="3"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
@@ -899,7 +1126,7 @@
       <c r="C19" s="1"/>
       <c r="D19" s="3"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="F19" s="3"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
@@ -909,7 +1136,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="3"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="F20" s="3"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
@@ -919,7 +1146,7 @@
       <c r="C21" s="1"/>
       <c r="D21" s="3"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="F21" s="3"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
@@ -929,7 +1156,7 @@
       <c r="C22" s="1"/>
       <c r="D22" s="3"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="F22" s="3"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
@@ -939,7 +1166,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="3"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="F23" s="3"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
@@ -949,7 +1176,7 @@
       <c r="C24" s="1"/>
       <c r="D24" s="3"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="F24" s="3"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
@@ -959,7 +1186,7 @@
       <c r="C25" s="1"/>
       <c r="D25" s="3"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
@@ -969,7 +1196,7 @@
       <c r="C26" s="1"/>
       <c r="D26" s="3"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="F26" s="3"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
@@ -979,7 +1206,7 @@
       <c r="C27" s="1"/>
       <c r="D27" s="4"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="F27" s="3"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
@@ -989,7 +1216,7 @@
       <c r="C28" s="1"/>
       <c r="D28" s="4"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
@@ -999,7 +1226,7 @@
       <c r="C29" s="1"/>
       <c r="D29" s="4"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="F29" s="3"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
@@ -1009,7 +1236,7 @@
       <c r="C30" s="1"/>
       <c r="D30" s="4"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="F30" s="3"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
@@ -1019,7 +1246,7 @@
       <c r="C31" s="1"/>
       <c r="D31" s="4"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="F31" s="3"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
@@ -1029,7 +1256,7 @@
       <c r="C32" s="1"/>
       <c r="D32" s="4"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+      <c r="F32" s="3"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
@@ -1039,7 +1266,7 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
+      <c r="F33" s="3"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
@@ -1049,7 +1276,7 @@
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
+      <c r="F34" s="3"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
@@ -1059,7 +1286,7 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
+      <c r="F35" s="3"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
@@ -1069,7 +1296,7 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
+      <c r="F36" s="3"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
@@ -1079,7 +1306,7 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
+      <c r="F37" s="3"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
@@ -1089,32 +1316,41 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
+      <c r="F38" s="3"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F40" s="3"/>
+    </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Terminid;Automatons; Illuminates" sqref="B2:B37" xr:uid="{D798BB62-A9AA-484F-B0C1-2284059A6DE0}">
       <formula1>"Terminids, Automatons, lluminate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C37:C38" xr:uid="{7F86A978-3145-4566-A41E-75F6734EC977}">
       <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I7" xr:uid="{8401F6A8-3ACC-45FE-A6B4-ABFE7E6BEC32}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I15" xr:uid="{8401F6A8-3ACC-45FE-A6B4-ABFE7E6BEC32}">
       <formula1>"No, Yes"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K7" xr:uid="{164DCC27-42E4-47D3-A8E6-BB0649B15D98}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K15" xr:uid="{164DCC27-42E4-47D3-A8E6-BB0649B15D98}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C7 F8:F39" xr:uid="{CBAA832B-00A1-4E19-BB8D-1F53FBB66E4C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C15" xr:uid="{CBAA832B-00A1-4E19-BB8D-1F53FBB66E4C}">
       <formula1>"N/A, Incineration Corps, Cyborgs, Predator Strain, Rupture Strain, Spore Burst Strain, Mindless Masses, Appropriators"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E7 C8:C36" xr:uid="{7FABB6A8-04E9-4E50-B186-49920BF7CE6B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C16:C36" xr:uid="{7FABB6A8-04E9-4E50-B186-49920BF7CE6B}">
       <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D36" xr:uid="{628F7E99-C793-498B-BB51-F86A87D5EBDA}">
       <formula1>"10, 9, 8, 7, 6, 5, 4, 3, 2, 1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E36" xr:uid="{EBD5F2ED-D181-416C-9F1A-012F13E9230E}">
+      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530E29EC-3056-4B23-B070-648578743D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D7D6EA-0296-472D-8CB8-81E3C4D11CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31010" yWindow="580" windowWidth="28800" windowHeight="15690" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="43">
   <si>
     <t>Mission Time</t>
   </si>
@@ -117,19 +117,73 @@
   </si>
   <si>
     <t>Eradicate</t>
+  </si>
+  <si>
+    <t>Mintoria</t>
+  </si>
+  <si>
+    <t>Sabotage Supply Bases</t>
+  </si>
+  <si>
+    <t>lluminate</t>
+  </si>
+  <si>
+    <t>Retrieve Valuable Data</t>
+  </si>
+  <si>
+    <t>Rirga Bay</t>
+  </si>
+  <si>
+    <t>Take Down Overship</t>
+  </si>
+  <si>
+    <t>Vote Snatchers</t>
+  </si>
+  <si>
+    <t>Repel Invasion</t>
+  </si>
+  <si>
+    <t>Evacuate High-Value Assets</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Incorrect mission type</t>
+  </si>
+  <si>
+    <t>Total Supercredits</t>
+  </si>
+  <si>
+    <t>Destroy Gazer Spire</t>
+  </si>
+  <si>
+    <t>Senge 23</t>
+  </si>
+  <si>
+    <t>Mindless Masses</t>
+  </si>
+  <si>
+    <t>UVP Alpha</t>
+  </si>
+  <si>
+    <t>Incorrect time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm:ss.0;@"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -155,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -164,9 +218,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -503,24 +554,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B874BC27-9F05-4CCB-84C0-24A63EA21ED1}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.26953125" customWidth="1"/>
     <col min="6" max="6" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.36328125" customWidth="1"/>
     <col min="9" max="9" width="4.90625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.1796875" customWidth="1"/>
+    <col min="14" max="14" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -557,8 +610,14 @@
       <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>46218</v>
       </c>
@@ -596,7 +655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>46218</v>
       </c>
@@ -633,8 +692,11 @@
       <c r="L3" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>46218</v>
       </c>
@@ -671,8 +733,11 @@
       <c r="L4" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N4" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>46218</v>
       </c>
@@ -709,8 +774,11 @@
       <c r="L5" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>46219</v>
       </c>
@@ -747,8 +815,11 @@
       <c r="L6" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N6" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>46219</v>
       </c>
@@ -786,7 +857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>46219</v>
       </c>
@@ -824,7 +895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>46219</v>
       </c>
@@ -862,7 +933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>46219</v>
       </c>
@@ -900,7 +971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>46219</v>
       </c>
@@ -938,7 +1009,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>46220</v>
       </c>
@@ -976,7 +1047,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>46220</v>
       </c>
@@ -1014,7 +1085,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>46220</v>
       </c>
@@ -1052,7 +1123,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>46220</v>
       </c>
@@ -1090,267 +1161,881 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L16" s="1">
+        <v>10</v>
+      </c>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1.6377314814814813E-2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L19" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20" s="1">
+        <v>11</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21" s="1">
+        <v>12</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22">
+        <v>10</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="3">
+        <v>7.7199074074074071E-3</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23">
+        <v>10</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2.361111111111111E-2</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L23" s="1">
+        <v>13</v>
+      </c>
+      <c r="M23">
+        <v>420</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24">
+        <v>10</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1.5497685185185186E-2</v>
+      </c>
+      <c r="G24" s="1">
+        <v>20</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L24" s="1">
+        <v>13</v>
+      </c>
+      <c r="M24">
+        <v>440</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25">
+        <v>10</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="1">
+        <v>14</v>
+      </c>
+      <c r="M25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="3">
+        <v>2.6388888888888889E-2</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="1">
+        <v>14</v>
+      </c>
+      <c r="M26">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="3">
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L27" s="1">
+        <v>14</v>
+      </c>
+      <c r="M27">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1.4490740740740742E-2</v>
+      </c>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L28" s="1">
+        <v>15</v>
+      </c>
+      <c r="M28">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="3">
+        <v>8.2638888888888883E-3</v>
+      </c>
+      <c r="G29" s="1">
+        <v>30</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L29" s="1">
+        <v>15</v>
+      </c>
+      <c r="M29">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1.6932870370370369E-2</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L30" s="1">
+        <v>15</v>
+      </c>
+      <c r="M30">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="3">
+        <v>8.1018518518518514E-3</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L31" s="1">
+        <v>16</v>
+      </c>
+      <c r="M31">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32">
+        <v>10</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="3">
+        <v>5.185185185185185E-3</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L32" s="1">
+        <v>16</v>
+      </c>
+      <c r="M32">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33">
+        <v>10</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1.3784722222222223E-2</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L33" s="1">
+        <v>16</v>
+      </c>
+      <c r="M33">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="3"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="3"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="3"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="3"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="3"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C39" s="1"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C40" s="1"/>
       <c r="F40" s="3"/>
     </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C41" s="1"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C42" s="1"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C43" s="1"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C44" s="1"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C45" s="1"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C46" s="1"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C47" s="1"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C48" s="1"/>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C49" s="1"/>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C50" s="1"/>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C51" s="1"/>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C52" s="1"/>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C53" s="1"/>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C54" s="1"/>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C55" s="1"/>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C56" s="1"/>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C57" s="1"/>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C58" s="1"/>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C59" s="1"/>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C60" s="1"/>
+    </row>
   </sheetData>
-  <dataValidations count="8">
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Terminid;Automatons; Illuminates" sqref="B2:B37" xr:uid="{D798BB62-A9AA-484F-B0C1-2284059A6DE0}">
       <formula1>"Terminids, Automatons, lluminate"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C37:C38" xr:uid="{7F86A978-3145-4566-A41E-75F6734EC977}">
-      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I15" xr:uid="{8401F6A8-3ACC-45FE-A6B4-ABFE7E6BEC32}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I18" xr:uid="{8401F6A8-3ACC-45FE-A6B4-ABFE7E6BEC32}">
       <formula1>"No, Yes"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K15" xr:uid="{164DCC27-42E4-47D3-A8E6-BB0649B15D98}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K18" xr:uid="{164DCC27-42E4-47D3-A8E6-BB0649B15D98}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C15" xr:uid="{CBAA832B-00A1-4E19-BB8D-1F53FBB66E4C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C18 C60" xr:uid="{CBAA832B-00A1-4E19-BB8D-1F53FBB66E4C}">
       <formula1>"N/A, Incineration Corps, Cyborgs, Predator Strain, Rupture Strain, Spore Burst Strain, Mindless Masses, Appropriators"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C16:C36" xr:uid="{7FABB6A8-04E9-4E50-B186-49920BF7CE6B}">
-      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D36" xr:uid="{628F7E99-C793-498B-BB51-F86A87D5EBDA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D40" xr:uid="{628F7E99-C793-498B-BB51-F86A87D5EBDA}">
       <formula1>"10, 9, 8, 7, 6, 5, 4, 3, 2, 1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E36" xr:uid="{EBD5F2ED-D181-416C-9F1A-012F13E9230E}">
-      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1" xr:uid="{5FCC0AFB-2BD9-4418-A011-81BD0E0B864E}">
+      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E20 E58:E59" xr:uid="{A02F080F-565E-4CBB-9F20-052DA9D7E4CF}">
+      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases, Take Down Overship"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C19:C59" xr:uid="{CD443ED4-E4BF-4C51-99FC-0D0F9FA657AD}">
+      <formula1>"N/A, Incineration Corps, Cyborgs, Predator Strain, Rupture Strain, Spore Burst Strain, Mindless Masses, Appropriators,Vote Snatchers"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21:E25 E57" xr:uid="{FED4EEA0-1D74-4EBF-A9E3-D929FD86EF61}">
+      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases, Take Down Overship, Repel Invasion"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E56" xr:uid="{7C4AB8FE-A995-45E4-A1F6-5AB74AD7C797}">
+      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases, Take Down Overship, Repel Invasion"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
